--- a/docs/descargas/encuesta_campo_robledo_8_hogares.xlsx
+++ b/docs/descargas/encuesta_campo_robledo_8_hogares.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encuesta (8 hogares)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Encuesta (8 hogares)'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Encuesta (8 hogares)'!$A$1:$L$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,12 +430,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
@@ -445,71 +445,65 @@
     <col width="38" customWidth="1" min="10" max="10"/>
     <col width="38" customWidth="1" min="11" max="11"/>
     <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="38" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Marca temporal</t>
+          <t>1. ¿Cuál es su edad?</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>1. ¿Cuál es su edad?</t>
+          <t>2. ¿Cuál es su sexo?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2. ¿Cuál es su sexo?</t>
+          <t>3. ¿En qué estrato está su vivienda?</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>3. ¿En qué estrato está su vivienda?</t>
+          <t>4. ¿En su hogar viven niños, niñas o adolescentes menores de 18 años?</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>4. ¿En su hogar viven niños, niñas o adolescentes menores de 18 años?</t>
+          <t>5. ¿Cuál es la situación laboral actual del jefe o jefa del hogar?</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>5. ¿Cuál es la situación laboral actual del jefe o jefa del hogar?</t>
+          <t>6. Los ingresos mensuales del hogar:</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>6. Los ingresos mensuales del hogar:</t>
+          <t>7. En los últimos 3 meses, por falta de dinero, ¿algún adulto del hogar se preocupó porque la comida se acabara?</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>7. En los últimos 3 meses, por falta de dinero, ¿algún adulto del hogar se preocupó porque la comida se acabara?</t>
+          <t>8. En ese mismo periodo, ¿algún adulto del hogar dejó de desayunar, almorzar o cenar por falta de dinero?</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>8. En ese mismo periodo, ¿algún adulto del hogar dejó de desayunar, almorzar o cenar por falta de dinero?</t>
+          <t>9. En ese mismo periodo, ¿algún adulto del hogar sintió hambre pero no comió por falta de dinero?</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>9. En ese mismo periodo, ¿algún adulto del hogar sintió hambre pero no comió por falta de dinero?</t>
+          <t>10. ¿Qué tanto cree que el tipo de trabajo del jefe o jefa del hogar afecta lo que el hogar puede comprar para comer?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>10. ¿Qué tanto cree que el tipo de trabajo del jefe o jefa del hogar afecta lo que el hogar puede comprar para comer?</t>
+          <t>11. Cuando el dinero no alcanza para la comida, ¿qué hace principalmente el hogar?</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>11. Cuando el dinero no alcanza para la comida, ¿qué hace principalmente el hogar?</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>12. En sus propias palabras, ¿cómo influye el trabajo del jefe o jefa del hogar en la alimentación de su familia?</t>
         </is>
@@ -518,37 +512,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026/10/21 12:00:22 p.m. GMT-5</t>
+          <t>45 a 59 años</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>45 a 59 años</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Estrato 1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Estrato 1</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Trabaja sin prestaciones o por cuenta propia</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Trabaja sin prestaciones o por cuenta propia</t>
+          <t>Apenas alcanzan para cubrir los gastos</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Apenas alcanzan para cubrir los gastos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -563,20 +557,15 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Algo</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Algo</t>
+          <t>Compra alimentos más baratos o de menor calidad</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Compra alimentos más baratos o de menor calidad</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Influye mucho mi trabajo pero hay ocasiones en las que no le da por tener otras deudad</t>
         </is>
@@ -585,37 +574,37 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026/10/21 12:06:15 p.m. GMT-5</t>
+          <t>45 a 59 años</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>45 a 59 años</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Estrato 2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Estrato 2</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Trabaja sin prestaciones o por cuenta propia</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Trabaja sin prestaciones o por cuenta propia</t>
+          <t>Apenas alcanzan para cubrir los gastos</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Apenas alcanzan para cubrir los gastos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -630,20 +619,15 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Algo</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Algo</t>
+          <t>Pide fiado o dinero prestado</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Pide fiado o dinero prestado</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Me toca trabajar más de 8 horas y trabajar lejos y llegar con la comida</t>
         </is>
@@ -652,37 +636,37 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026/10/21 12:24:16 p.m. GMT-5</t>
+          <t>30 a 44 años</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>30 a 44 años</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Estrato 2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Estrato 2</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
+          <t>Apenas alcanzan para cubrir los gastos</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Apenas alcanzan para cubrir los gastos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -697,20 +681,15 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mucho</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Mucho</t>
+          <t>Reduce las porciones o las comidas</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Reduce las porciones o las comidas</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Afecta mucho ya que si no trabaja no hay comida</t>
         </is>
@@ -719,37 +698,37 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026/10/21 12:27:37 p.m. GMT-5</t>
+          <t>45 a 59 años</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>45 a 59 años</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Estrato 3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Estrato 3</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
+          <t>No alcanzan para cubrir los gastos del mes</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>No alcanzan para cubrir los gastos del mes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -764,20 +743,15 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poco</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Poco</t>
+          <t>No hace ninguna de estas cosas</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>No hace ninguna de estas cosas</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Es un complemento </t>
         </is>
@@ -786,65 +760,60 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026/10/21 12:33:18 p.m. GMT-5</t>
+          <t>18 a 29 años</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18 a 29 años</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Estrato 2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Estrato 2</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
+          <t>Apenas alcanzan para cubrir los gastos</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Apenas alcanzan para cubrir los gastos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mucho</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Mucho</t>
+          <t>Pide fiado o dinero prestado</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Pide fiado o dinero prestado</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Mucho porque dependo del jefe de hogar para comer</t>
         </is>
@@ -853,37 +822,37 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026/10/21 12:37:23 p.m. GMT-5</t>
+          <t>45 a 59 años</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>45 a 59 años</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Estrato 3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Estrato 3</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Trabaja sin prestaciones o por cuenta propia</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Trabaja sin prestaciones o por cuenta propia</t>
+          <t>Apenas alcanzan para cubrir los gastos</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Apenas alcanzan para cubrir los gastos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -898,20 +867,15 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>No hace ninguna de estas cosas</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>No hace ninguna de estas cosas</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Balanceada, me alcanza para todo</t>
         </is>
@@ -920,37 +884,37 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026/10/21 6:04:35 p.m. GMT-5</t>
+          <t>18 a 29 años</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>18 a 29 años</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Estrato 3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Estrato 3</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
+          <t>Alcanzan y a veces sobra algo</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Alcanzan y a veces sobra algo</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -965,20 +929,15 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Algo</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Algo</t>
+          <t>No hace ninguna de estas cosas</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>No hace ninguna de estas cosas</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Bastante, pero mientras se tenga un buen trabajo y ganas de salir adelante, no hay problema. </t>
         </is>
@@ -987,37 +946,37 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026/10/21 6:14:23 p.m. GMT-5</t>
+          <t>30 a 44 años</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>30 a 44 años</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Estrato 2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Estrato 2</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Trabaja con contrato y prestaciones (salud y pensión)</t>
+          <t>Apenas alcanzan para cubrir los gastos</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Apenas alcanzan para cubrir los gastos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,27 +991,22 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mucho</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Mucho</t>
+          <t>Compra alimentos más baratos o de menor calidad</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Compra alimentos más baratos o de menor calidad</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Gracias a Dios nunca me ha faltado nada, pero trabajar es importante para llevar comida a casa. </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:L9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>